--- a/Nalanda_IML_CN_Reconciliation_FY2526.xlsx
+++ b/Nalanda_IML_CN_Reconciliation_FY2526.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1345" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="574">
   <si>
     <t>NALANDA ENTERPRISES vs IML (boAt) – Credit Note Reconciliation FY Apr'25 to Mar'26</t>
   </si>
@@ -308,19 +308,16 @@
     <t>30 incremental WOD outlets × ₹50 = ₹1,500 w/GST; settled 7 months late</t>
   </si>
   <si>
-    <t>PRIMARY &amp; SECONDARY CNs – AMOUNTS IN EXCEL/PDF ATTACHMENTS (NOT READABLE VIA EMAIL)</t>
-  </si>
-  <si>
-    <t>These amounts must be verified by opening the attached Excel/PDF in each settlement email.</t>
-  </si>
-  <si>
-    <t>These amounts must be verified by opening the attached Excel/PDF in each settlement email. See EMAIL REGISTER tab for thread links.</t>
+    <t>PRIMARY &amp; SECONDARY CNs (Oct'25–Mar'26) – CONFIRMED VIA PDF FILENAME → SAP DOC# MATCHING</t>
+  </si>
+  <si>
+    <t>From Oct'25 onwards IML named PDFs with CN doc# embedded (e.g. 76_7272651637_Nalanda_Enterprises_Secondary_CN.pdf). These doc# matched exactly to SAP statement entries, confirming amounts without opening files. Apr-Sep'25 PDFs used generic names – amounts still need manual verification from attachments.</t>
   </si>
   <si>
     <t>OPEN ISSUES &amp; PENDING CNs</t>
   </si>
   <si>
-    <t>Audio Tieup Nov'25 – DISPUTED</t>
+    <t>Audio Tieup Nov'25 – DISPUTED ⚠</t>
   </si>
   <si>
     <t>₹80,639.92 CN received but Atinder Singh questioned if already settled against prior commitment. Abhishek Roshan said 'Will discuss' in Dec'25. As of Jun 30, 2026, Lavesh is still awaiting clarification from IML. Email thread: 19b6f83de9fbb445</t>
@@ -329,31 +326,43 @@
     <t>Primary CN Mar'25 – UNRESOLVED</t>
   </si>
   <si>
-    <t>Primary CN for Mar'25 settled Apr'25 (email 1964489f47562bbe) but Lavesh has been following up Jun'25, Dec'25, Apr'26 with no response. Amount unknown without reading attachment.</t>
-  </si>
-  <si>
-    <t>Nirvana Series Jul'25 – DELAYED</t>
-  </si>
-  <si>
-    <t>CN for Jul'25 billing was settled only in Apr'26 (9-month delay). Amount in PDF attachment. Thread: 19d8bb74bfeca5c8</t>
-  </si>
-  <si>
-    <t>Nirvana Series Sep'25 – DELAYED</t>
-  </si>
-  <si>
-    <t>CN for Sep'25 billing was settled only in Apr'26 (7-month delay). Amount in PDF attachment. Thread: 19d8bb8eadd4ce30</t>
-  </si>
-  <si>
-    <t>WOD FOS Sep'25 – DELAYED</t>
-  </si>
-  <si>
-    <t>CN settled Apr'26, amount ₹1,271.19. Confirmed. 7-month delay.</t>
+    <t>Primary CN for Mar'25 settled Apr'25 (email 1964489f47562bbe) but Lavesh has been following up Jun'25, Dec'25, Apr'26 with no response. Amount unknown – open PDF in email attachment to verify (likely DG 4127260399 ₹16,78,339.89 from statement).</t>
+  </si>
+  <si>
+    <t>Secondary CN Mar'25 – NEED ATTACHMENT</t>
+  </si>
+  <si>
+    <t>Amount unknown – open PDF in email thread 1961ea230969c552. Likely DG 4127260096 ₹2,37,254 from statement.</t>
+  </si>
+  <si>
+    <t>Apr-Sep'25 Primary/Secondary – NEED ATTACHMENT</t>
+  </si>
+  <si>
+    <t>6 months × 2 types = 12 email threads where PDF used generic name 'Nalanda Enterprises.pdf' (no doc# embedded). Amounts must be manually verified by opening attachments in Gmail threads listed in EMAIL REGISTER tab.</t>
+  </si>
+  <si>
+    <t>Nirvana Series Jul'25 – DELAYED + NEED ATTACHMENT</t>
+  </si>
+  <si>
+    <t>CN for Jul'25 billing settled only in Apr'26 (9-month delay). Amount in PDF attachment. Thread: 19d8bb74bfeca5c8</t>
+  </si>
+  <si>
+    <t>Nirvana Series Sep'25 – DELAYED + NEED ATTACHMENT</t>
+  </si>
+  <si>
+    <t>CN for Sep'25 billing settled only in Apr'26 (7-month delay). Amount in PDF attachment. Thread: 19d8bb8eadd4ce30</t>
+  </si>
+  <si>
+    <t>Slab Sep'25 &amp; Nov'25 – NEED ATTACHMENT</t>
+  </si>
+  <si>
+    <t>Slab &amp; Combo CNs for Sep'25 (thread 199f1777512ea782) and Nov'25 (thread 19b6f743900b20b6) amounts need Excel attachment verification. Oct'25 Slab confirmed ₹3,01,750.</t>
   </si>
   <si>
     <t>Secondary CN Mar'26 – PENDING</t>
   </si>
   <si>
-    <t>Mar'26 email (16-May-26) explicitly states 'Secondary CN for Mar'26 will be settled with Apr'26'. Still pending as of Jun 30, 2026.</t>
+    <t>Mar'26 email (16-May-26) explicitly states 'Secondary CN for Mar'26 will be settled with Apr'26'. Estimated from May'26 statement: CNs 7272713707+7062700955+7272714094 = ₹3,56,135.63. Still pending confirmation as of Jun 30, 2026.</t>
   </si>
   <si>
     <t>TOT Q4 JFM'26 – NOT FOUND</t>
@@ -368,12 +377,6 @@
     <t>Slab/Combo CN for Jan'26 not yet located in email search. Need to search specifically.</t>
   </si>
   <si>
-    <t>Primary/Secondary amounts – NOT READABLE</t>
-  </si>
-  <si>
-    <t>For months Apr'25 to Mar'26 (18 email threads), CN amounts are in Excel/PDF attachments only. To complete reconciliation, Lavesh needs to provide the amounts from those attachments or download them from Gmail.</t>
-  </si>
-  <si>
     <t>EMAIL REGISTER – IML CN Settlement Emails (Gmail: lavesh.bansal@nalandaenterprises.com)</t>
   </si>
   <si>
@@ -569,7 +572,7 @@
     <t>19c7624197529deb</t>
   </si>
   <si>
-    <t>PDF/Excel; Secondary settled separately per note</t>
+    <t>CONFIRMED VIA DOC# MATCH: Primary ₹6,94,031.89 (CNs 7292600102+7062602199+7062602342+7062602387+7062602443+7272651145+7272651261+7272651282+7272651511+7272651670+7272651976+DG 4106262828) + Secondary ₹4,83,582.73 (CNs 7272651637+7272651898+DG 4106262873). Secondary excl. GST per note.</t>
   </si>
   <si>
     <t>13-Feb-26</t>
@@ -581,6 +584,9 @@
     <t>19c570ac7e6fe741</t>
   </si>
   <si>
+    <t>CONFIRMED VIA DOC# MATCH: Primary ₹1,46,091.33 (CNs 7062602826+7062602862+7272660288+7272660340+7272660422) + Secondary ₹54,419.49 (ZC 1626003911). Secondary excl. GST per note.</t>
+  </si>
+  <si>
     <t>30-Jan-26</t>
   </si>
   <si>
@@ -590,6 +596,9 @@
     <t>19c0db8489529d82</t>
   </si>
   <si>
+    <t>CONFIRMED VIA DOC# MATCH: CN 7272673455 (₹65) + CN 7272673966 (₹1,44,108.76) + ZC 1626003680 (₹49,472) + ZC 1626003473 (₹14,726) = ₹2,08,371.76. DNs 9272648183/9062639291/9272648064/9272648117 excluded (debit notes).</t>
+  </si>
+  <si>
     <t>11-Mar-26</t>
   </si>
   <si>
@@ -599,7 +608,7 @@
     <t>19cdd18f184f569f</t>
   </si>
   <si>
-    <t>PDF/Excel; Secondary separately</t>
+    <t>CONFIRMED VIA DOC# MATCH: Primary ₹2,88,688.00 (CNs 7062603510+7062603592+7062603716+7062603757+7272682679+7272682911+7272682954+7272683006+7272683050+7272683163+7272683224) + Secondary ₹36,493.37 (CN 7272682724+ZC 1626004093+ZC 1626004143). Secondary excl. GST per note.</t>
   </si>
   <si>
     <t>02-Apr-26</t>
@@ -611,6 +620,9 @@
     <t>19d4cee3f816871a</t>
   </si>
   <si>
+    <t>CONFIRMED VIA DOC# MATCH: CNs 7062603900+7062603920+7062603980+7062604009+7062604073+7062604107+7272691140+7272691160+7272691167+7272691275+7272691288+7272691337+7272691451+7272691575+7272691603+7272691621. All 16 CNs from Mar'26 posting match PDF filenames in email.</t>
+  </si>
+  <si>
     <t>16-May-26</t>
   </si>
   <si>
@@ -620,7 +632,7 @@
     <t>19e31b7d5b88dc5b</t>
   </si>
   <si>
-    <t>NOTE: Secondary CN for Mar'26 will be settled with Apr'26 → PENDING</t>
+    <t>CONFIRMED VIA DOC# MATCH (Primary only): CNs 7062700490+7062700534+7272707182+7272707208+7272707316+7272707360+7272707411+7272707412+7272707461+7292700034+7292700038 from Apr'26 posting = ₹8,13,547.03. NOTE: Secondary CN for Mar'26 PENDING – to be settled with Apr'26 (May'26 stmt: CNs 7272713707+7062700955+7272714094 = ₹3,56,135.63)</t>
   </si>
   <si>
     <t>PART 2: SLAB &amp; COMBO SCHEME CNs</t>
@@ -1654,7 +1666,7 @@
     <t>DELAYED 7 months. Verify from PDF thread 19d8bb8eadd4ce30</t>
   </si>
   <si>
-    <t>DG 4106262828 (₹2,51,530) + DG 4106262873 (₹1,71,317.85) = ₹4,22,847.85 – but need to verify these are Oct'25. Thread 19c7624197529deb</t>
+    <t>✓ CONFIRMED VIA DOC# MATCH – Primary ₹6,94,031.89 (12 CNs/DGs) + Secondary ₹4,83,582.73 (3 CNs/DGs). All doc# matched from PDF filenames to SAP statement. Secondary excl. GST.</t>
   </si>
   <si>
     <t>✓ CONFIRMED – DG 4106261557 (₹2,77,000) + DG 4106261599 (₹18,750) + DG 4106261625 (₹6,000)</t>
@@ -1663,10 +1675,7 @@
     <t>✓ CONFIRMED – DG 4106261508</t>
   </si>
   <si>
-    <t>See Nov'25 CNs</t>
-  </si>
-  <si>
-    <t>Verify from attachment thread 19c570ac7e6fe741. Nov'25 CN 7272651898 (₹2,74,573.80) may be part of it</t>
+    <t>✓ CONFIRMED VIA DOC# MATCH – Primary ₹1,46,091.33 (5 CNs) + Secondary ₹54,419.49 (ZC 1626003911). All doc# matched. Secondary excl. GST.</t>
   </si>
   <si>
     <t>DG 4106261823 (₹3,57,103) + DG 4106261876 (₹36,000) + DG 4106261897 (₹36,385) = ₹4,29,488 – verify Excel thread 19b6f743900b20b6</t>
@@ -1684,25 +1693,16 @@
     <t>✓ CONFIRMED – DG 4106262947 (₹1,47,944.61) + DG 4106262951 (₹92,400)</t>
   </si>
   <si>
-    <t>See Jan'26 + Mar'26</t>
-  </si>
-  <si>
-    <t>ZC 1626003680 (₹49,472) + CN 7272673966 (₹1,44,108.76) + ZC 1626003911 (₹54,419.49) may be Dec'25. Also Mar'26 CNs. Thread 19c0db8489529d82</t>
-  </si>
-  <si>
-    <t>See Mar'26 statement</t>
-  </si>
-  <si>
-    <t>Mar'26 has CN 7272691167 (₹1,23,759) + CN 7272691337 (₹2,01,920) + others – likely Jan'26 scheme. Thread 19cdd18f184f569f</t>
-  </si>
-  <si>
-    <t>Apr'26 CNs likely include Feb'26 scheme. Thread 19d4cee3f816871a</t>
-  </si>
-  <si>
-    <t>See May'26 statement</t>
-  </si>
-  <si>
-    <t>May'26 CNs (₹3,56,335) likely for Mar'26. Thread 19e31b7d5b88dc5b. Secondary PENDING – to come with Apr'26 settlement</t>
+    <t>✓ CONFIRMED VIA DOC# MATCH – CN 7272673455 (₹65) + CN 7272673966 (₹1,44,108.76) + ZC 1626003680 (₹49,472) + ZC 1626003473 (₹14,726). DNs excluded.</t>
+  </si>
+  <si>
+    <t>✓ CONFIRMED VIA DOC# MATCH – Primary ₹2,88,688 (11 CNs) + Secondary ₹36,493.37 (CN 7272682724 + ZC 1626004093 + ZC 1626004143). Secondary excl. GST.</t>
+  </si>
+  <si>
+    <t>✓ CONFIRMED VIA DOC# MATCH – 16 CNs from Mar'26 posting (7062603900 to 7272691621). All PDF filenames contained CN doc# matching SAP statement.</t>
+  </si>
+  <si>
+    <t>✓ CONFIRMED (Primary) VIA DOC# MATCH – 11 CNs from Apr'26 posting = ₹8,13,547.03. Secondary PENDING: May'26 CNs 7272713707+7062700955+7272714094 = ₹3,56,135.63 to be settled with Apr'26.</t>
   </si>
   <si>
     <t>NALANDA TALLY PRIMARY BILLING SUMMARY (IMAGINE_27) – FY Apr'25 to Mar'26</t>
@@ -1803,7 +1803,7 @@
     <font>
       <i/>
       <sz val="11"/>
-      <color rgb="FFCC0000"/>
+      <color rgb="FF375623"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1817,7 +1817,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1850,7 +1850,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF6600"/>
+        <fgColor rgb="FF375623"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1875,6 +1875,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6600"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1974,7 +1980,7 @@
     <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2272,7 +2278,7 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -2971,7 +2977,7 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
@@ -2983,15 +2989,15 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" s="20" t="s">
         <v>100</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>101</v>
       </c>
       <c r="C43" s="20"/>
       <c r="D43" s="20"/>
@@ -3002,10 +3008,10 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" s="20" t="s">
         <v>102</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>103</v>
       </c>
       <c r="C44" s="20"/>
       <c r="D44" s="20"/>
@@ -3016,10 +3022,10 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="20" t="s">
         <v>104</v>
-      </c>
-      <c r="B45" s="20" t="s">
-        <v>105</v>
       </c>
       <c r="C45" s="20"/>
       <c r="D45" s="20"/>
@@ -3030,10 +3036,10 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="B46" s="20" t="s">
         <v>106</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>107</v>
       </c>
       <c r="C46" s="20"/>
       <c r="D46" s="20"/>
@@ -3044,10 +3050,10 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B47" s="20" t="s">
         <v>108</v>
-      </c>
-      <c r="B47" s="20" t="s">
-        <v>109</v>
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="20"/>
@@ -3058,10 +3064,10 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" s="20" t="s">
         <v>110</v>
-      </c>
-      <c r="B48" s="20" t="s">
-        <v>111</v>
       </c>
       <c r="C48" s="20"/>
       <c r="D48" s="20"/>
@@ -3072,10 +3078,10 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B49" s="20" t="s">
         <v>112</v>
-      </c>
-      <c r="B49" s="20" t="s">
-        <v>113</v>
       </c>
       <c r="C49" s="20"/>
       <c r="D49" s="20"/>
@@ -3086,10 +3092,10 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B50" s="20" t="s">
         <v>114</v>
-      </c>
-      <c r="B50" s="20" t="s">
-        <v>115</v>
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="20"/>
@@ -3100,10 +3106,10 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" s="20" t="s">
         <v>116</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>117</v>
       </c>
       <c r="C51" s="20"/>
       <c r="D51" s="20"/>
@@ -3112,8 +3118,22 @@
       <c r="G51" s="20"/>
       <c r="H51" s="20"/>
     </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+    </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="E6:H6"/>
@@ -3142,6 +3162,7 @@
     <mergeCell ref="B49:H49"/>
     <mergeCell ref="B50:H50"/>
     <mergeCell ref="B51:H51"/>
+    <mergeCell ref="B52:H52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3166,7 +3187,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3180,27 +3201,27 @@
         <v>38</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C2" s="21" t="s">
         <v>39</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -3211,48 +3232,48 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="20" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="20" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3260,22 +3281,22 @@
         <v>7</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -3283,22 +3304,22 @@
         <v>7</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3306,22 +3327,22 @@
         <v>9</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -3329,22 +3350,22 @@
         <v>9</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3352,22 +3373,22 @@
         <v>11</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3375,22 +3396,22 @@
         <v>11</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3398,22 +3419,22 @@
         <v>13</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3421,22 +3442,22 @@
         <v>13</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3444,22 +3465,22 @@
         <v>15</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3467,22 +3488,22 @@
         <v>15</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -3490,22 +3511,22 @@
         <v>17</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3513,165 +3534,165 @@
         <v>17</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="C18" s="20" t="s">
+      <c r="B18" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="C18" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="D18" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="F18" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="G18" s="20" t="s">
+      <c r="E18" s="13" t="s">
         <v>183</v>
       </c>
+      <c r="F18" s="14">
+        <v>1177614.62</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="D19" s="20" t="s">
+      <c r="B19" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="D19" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="F19" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>183</v>
+      <c r="E19" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="F19" s="14">
+        <v>200510.82</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="E20" s="20" t="s">
+      <c r="B20" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="F20" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>183</v>
+      <c r="D20" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F20" s="14">
+        <v>208371.76</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="G21" s="20" t="s">
+      <c r="B21" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>193</v>
       </c>
+      <c r="D21" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="F21" s="14">
+        <v>325181.37</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>193</v>
+      <c r="B22" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="F22" s="14">
+        <v>599237.86</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>200</v>
+      <c r="B23" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="F23" s="23">
+        <v>813547.03</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="22" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
@@ -3685,22 +3706,22 @@
         <v>17</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3708,22 +3729,22 @@
         <v>19</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F26" s="14">
         <v>301750</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3731,22 +3752,22 @@
         <v>21</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3754,27 +3775,27 @@
         <v>25</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G28" s="20" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="22" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
@@ -3788,22 +3809,22 @@
         <v>13</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>51</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F30" s="14">
         <v>16993.23</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3811,22 +3832,22 @@
         <v>17</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>58</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F31" s="14">
         <v>292965.64</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3834,22 +3855,22 @@
         <v>19</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>71</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F32" s="14">
         <v>370486.77</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3857,22 +3878,22 @@
         <v>21</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>80</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F33" s="16">
         <v>80639.92</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3880,22 +3901,22 @@
         <v>75</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>76</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F34" s="14">
         <v>663182.4399999999</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3903,22 +3924,22 @@
         <v>21</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>85</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F35" s="14">
         <v>150000</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3926,27 +3947,27 @@
         <v>13</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="22" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
@@ -3960,22 +3981,22 @@
         <v>17</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3983,22 +4004,22 @@
         <v>17</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>93</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="F39" s="14">
         <v>1271.19</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -4006,22 +4027,22 @@
         <v>45</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C40" s="13" t="s">
         <v>46</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F40" s="14">
         <v>221823.28</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -4029,45 +4050,45 @@
         <v>21</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>89</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F41" s="14">
         <v>240344.61</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="23" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F42" s="23" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G42" s="23" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -4099,7 +4120,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4110,7 +4131,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4124,22 +4145,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4147,22 +4168,22 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E5" s="7">
         <v>237254</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4170,22 +4191,22 @@
         <v>7</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E6" s="24">
         <v>21490</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4193,22 +4214,22 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E7" s="7">
         <v>1678339.89</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -4219,16 +4240,16 @@
         <v>46</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E8" s="7">
         <v>221823.28</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>45</v>
@@ -4242,24 +4263,24 @@
         <v>46</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E9" s="24">
         <v>80772</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="22" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B10" s="25"/>
       <c r="C10" s="25"/>
@@ -4275,19 +4296,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E11" s="7">
         <v>140215.66</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>7</v>
@@ -4298,19 +4319,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E12" s="24">
         <v>236915.25</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>7</v>
@@ -4318,7 +4339,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="22" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
@@ -4334,19 +4355,19 @@
         <v>11</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E14" s="24">
         <v>182215.66</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>9</v>
@@ -4357,22 +4378,22 @@
         <v>11</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E15" s="24">
         <v>92283.77</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4380,19 +4401,19 @@
         <v>11</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E16" s="24">
         <v>727990.39</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>11</v>
@@ -4403,27 +4424,27 @@
         <v>11</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E17" s="24">
         <v>110211.86</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="22" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B18" s="25"/>
       <c r="C18" s="25"/>
@@ -4439,22 +4460,22 @@
         <v>13</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E19" s="24">
         <v>90000</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -4462,19 +4483,19 @@
         <v>13</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E20" s="24">
         <v>156950</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>11</v>
@@ -4485,19 +4506,19 @@
         <v>13</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E21" s="24">
         <v>438423.5</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="G21" s="20" t="s">
         <v>13</v>
@@ -4508,19 +4529,19 @@
         <v>13</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E22" s="24">
         <v>19279.66</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G22" s="20" t="s">
         <v>11</v>
@@ -4531,19 +4552,19 @@
         <v>13</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E23" s="24">
         <v>129690.69</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G23" s="20" t="s">
         <v>13</v>
@@ -4551,7 +4572,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="22" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
@@ -4567,19 +4588,19 @@
         <v>15</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E25" s="24">
         <v>28008.47</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>13</v>
@@ -4590,19 +4611,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E26" s="24">
         <v>360675.54</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="G26" s="20" t="s">
         <v>15</v>
@@ -4610,7 +4631,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="22" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
@@ -4626,19 +4647,19 @@
         <v>17</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E28" s="24">
         <v>124073.78</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="G28" s="20" t="s">
         <v>15</v>
@@ -4649,19 +4670,19 @@
         <v>17</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E29" s="24">
         <v>161455.5</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="G29" s="20" t="s">
         <v>17</v>
@@ -4672,19 +4693,19 @@
         <v>17</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E30" s="14">
         <v>13490.81</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>13</v>
@@ -4695,19 +4716,19 @@
         <v>17</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E31" s="14">
         <v>3502.42</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>13</v>
@@ -4718,22 +4739,22 @@
         <v>17</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E32" s="24">
         <v>3800</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -4741,19 +4762,19 @@
         <v>17</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E33" s="24">
         <v>77669.49000000001</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="G33" s="20" t="s">
         <v>15</v>
@@ -4764,27 +4785,27 @@
         <v>17</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E34" s="24">
         <v>19939.43</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="22" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -4803,16 +4824,16 @@
         <v>58</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E36" s="7">
         <v>86525.42</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>17</v>
@@ -4826,16 +4847,16 @@
         <v>58</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E37" s="7">
         <v>107415</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="G37" s="8" t="s">
         <v>17</v>
@@ -4849,16 +4870,16 @@
         <v>58</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E38" s="7">
         <v>20000</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>17</v>
@@ -4872,16 +4893,16 @@
         <v>58</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E39" s="14">
         <v>292965.64</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="G39" s="13" t="s">
         <v>17</v>
@@ -4892,19 +4913,19 @@
         <v>19</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E40" s="24">
         <v>657603.58</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="G40" s="20" t="s">
         <v>17</v>
@@ -4912,7 +4933,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="22" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
@@ -4928,19 +4949,19 @@
         <v>21</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E42" s="24">
         <v>228008.72</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G42" s="20" t="s">
         <v>19</v>
@@ -4951,19 +4972,19 @@
         <v>21</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E43" s="24">
         <v>20999.99</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G43" s="20" t="s">
         <v>19</v>
@@ -4974,19 +4995,19 @@
         <v>21</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E44" s="24">
         <v>15426.87</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G44" s="20" t="s">
         <v>19</v>
@@ -4997,19 +5018,19 @@
         <v>21</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E45" s="24">
         <v>36000.15</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G45" s="20" t="s">
         <v>19</v>
@@ -5020,19 +5041,19 @@
         <v>21</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E46" s="24">
         <v>1000.17</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="G46" s="20" t="s">
         <v>19</v>
@@ -5043,19 +5064,19 @@
         <v>21</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E47" s="24">
         <v>31500.33</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G47" s="20" t="s">
         <v>19</v>
@@ -5066,19 +5087,19 @@
         <v>21</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E48" s="24">
         <v>41005</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G48" s="20" t="s">
         <v>19</v>
@@ -5089,19 +5110,19 @@
         <v>21</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E49" s="24">
         <v>20000.06</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>19</v>
@@ -5112,19 +5133,19 @@
         <v>21</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E50" s="24">
         <v>20999.81</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G50" s="20" t="s">
         <v>19</v>
@@ -5135,19 +5156,19 @@
         <v>21</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E51" s="24">
         <v>37691.08</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G51" s="20" t="s">
         <v>19</v>
@@ -5158,19 +5179,19 @@
         <v>21</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E52" s="24">
         <v>23000.56</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G52" s="20" t="s">
         <v>19</v>
@@ -5181,19 +5202,19 @@
         <v>21</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E53" s="24">
         <v>274573.8</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="G53" s="20" t="s">
         <v>19</v>
@@ -5204,19 +5225,19 @@
         <v>21</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E54" s="7">
         <v>4560.23</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G54" s="8" t="s">
         <v>19</v>
@@ -5227,19 +5248,19 @@
         <v>21</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E55" s="14">
         <v>370486.77</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>19</v>
@@ -5250,19 +5271,19 @@
         <v>21</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E56" s="14">
         <v>277000</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>19</v>
@@ -5273,19 +5294,19 @@
         <v>21</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E57" s="14">
         <v>18750</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G57" s="13" t="s">
         <v>19</v>
@@ -5296,19 +5317,19 @@
         <v>21</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E58" s="14">
         <v>6000</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>19</v>
@@ -5316,7 +5337,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="22" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B59" s="25"/>
       <c r="C59" s="25"/>
@@ -5332,19 +5353,19 @@
         <v>23</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E60" s="14">
         <v>663182.4399999999</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G60" s="13" t="s">
         <v>75</v>
@@ -5358,16 +5379,16 @@
         <v>80</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E61" s="7">
         <v>357103</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="G61" s="8" t="s">
         <v>21</v>
@@ -5381,16 +5402,16 @@
         <v>80</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E62" s="7">
         <v>36000</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="G62" s="8" t="s">
         <v>21</v>
@@ -5404,16 +5425,16 @@
         <v>80</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E63" s="14">
         <v>80639.92</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="G63" s="13" t="s">
         <v>21</v>
@@ -5427,16 +5448,16 @@
         <v>76</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E64" s="7">
         <v>36385</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="G64" s="8" t="s">
         <v>21</v>
@@ -5450,16 +5471,16 @@
         <v>76</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E65" s="14">
         <v>150000</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>21</v>
@@ -5473,16 +5494,16 @@
         <v>76</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D66" s="20" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E66" s="24">
         <v>16199.34</v>
       </c>
       <c r="F66" s="20" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G66" s="20" t="s">
         <v>21</v>
@@ -5496,16 +5517,16 @@
         <v>76</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D67" s="20" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E67" s="24">
         <v>74290.78</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>21</v>
@@ -5519,16 +5540,16 @@
         <v>76</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D68" s="20" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E68" s="24">
         <v>14900.75</v>
       </c>
       <c r="F68" s="20" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G68" s="20" t="s">
         <v>21</v>
@@ -5542,16 +5563,16 @@
         <v>76</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D69" s="20" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="E69" s="24">
         <v>14700.34</v>
       </c>
       <c r="F69" s="20" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G69" s="20" t="s">
         <v>21</v>
@@ -5565,16 +5586,16 @@
         <v>76</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D70" s="20" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E70" s="24">
         <v>26000.12</v>
       </c>
       <c r="F70" s="20" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G70" s="20" t="s">
         <v>21</v>
@@ -5585,19 +5606,19 @@
         <v>23</v>
       </c>
       <c r="B71" s="20" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D71" s="20" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E71" s="24">
         <v>14726</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="G71" s="20" t="s">
         <v>21</v>
@@ -5605,7 +5626,7 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="22" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B72" s="25"/>
       <c r="C72" s="25"/>
@@ -5621,19 +5642,19 @@
         <v>25</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D73" s="20" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E73" s="24">
         <v>49472</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="G73" s="20" t="s">
         <v>23</v>
@@ -5644,22 +5665,22 @@
         <v>25</v>
       </c>
       <c r="B74" s="20" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D74" s="20" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E74" s="24">
         <v>65</v>
       </c>
       <c r="F74" s="20" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="G74" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -5667,19 +5688,19 @@
         <v>25</v>
       </c>
       <c r="B75" s="20" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D75" s="20" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E75" s="24">
         <v>144108.76</v>
       </c>
       <c r="F75" s="20" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="G75" s="20" t="s">
         <v>23</v>
@@ -5690,19 +5711,19 @@
         <v>25</v>
       </c>
       <c r="B76" s="20" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D76" s="20" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E76" s="24">
         <v>54419.49</v>
       </c>
       <c r="F76" s="20" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="G76" s="20" t="s">
         <v>23</v>
@@ -5713,19 +5734,19 @@
         <v>25</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E77" s="14">
         <v>1271.19</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="G77" s="13" t="s">
         <v>17</v>
@@ -5733,7 +5754,7 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="22" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B78" s="25"/>
       <c r="C78" s="25"/>
@@ -5749,19 +5770,19 @@
         <v>27</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D79" s="20" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E79" s="24">
         <v>22749.15</v>
       </c>
       <c r="F79" s="20" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="G79" s="20" t="s">
         <v>25</v>
@@ -5772,19 +5793,19 @@
         <v>27</v>
       </c>
       <c r="B80" s="20" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D80" s="20" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E80" s="24">
         <v>3791.53</v>
       </c>
       <c r="F80" s="20" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="G80" s="20" t="s">
         <v>25</v>
@@ -5795,19 +5816,19 @@
         <v>27</v>
       </c>
       <c r="B81" s="20" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D81" s="20" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E81" s="24">
         <v>251530</v>
       </c>
       <c r="F81" s="20" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="G81" s="20" t="s">
         <v>19</v>
@@ -5818,19 +5839,19 @@
         <v>27</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D82" s="20" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E82" s="24">
         <v>171317.85</v>
       </c>
       <c r="F82" s="20" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="G82" s="20" t="s">
         <v>19</v>
@@ -5841,19 +5862,19 @@
         <v>27</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E83" s="14">
         <v>147944.61</v>
       </c>
       <c r="F83" s="13" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="G83" s="13" t="s">
         <v>21</v>
@@ -5864,19 +5885,19 @@
         <v>27</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E84" s="14">
         <v>92400</v>
       </c>
       <c r="F84" s="13" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="G84" s="13" t="s">
         <v>21</v>
@@ -5887,19 +5908,19 @@
         <v>27</v>
       </c>
       <c r="B85" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D85" s="20" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E85" s="24">
         <v>69909.02</v>
       </c>
       <c r="F85" s="20" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G85" s="20" t="s">
         <v>21</v>
@@ -5910,19 +5931,19 @@
         <v>27</v>
       </c>
       <c r="B86" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D86" s="20" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E86" s="24">
         <v>62614.93</v>
       </c>
       <c r="F86" s="20" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G86" s="20" t="s">
         <v>21</v>
@@ -5933,19 +5954,19 @@
         <v>27</v>
       </c>
       <c r="B87" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D87" s="20" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E87" s="24">
         <v>9798.190000000001</v>
       </c>
       <c r="F87" s="20" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G87" s="20" t="s">
         <v>21</v>
@@ -5956,19 +5977,19 @@
         <v>27</v>
       </c>
       <c r="B88" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C88" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D88" s="20" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E88" s="24">
         <v>10464.28</v>
       </c>
       <c r="F88" s="20" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G88" s="20" t="s">
         <v>21</v>
@@ -5979,19 +6000,19 @@
         <v>27</v>
       </c>
       <c r="B89" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D89" s="20" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E89" s="24">
         <v>29388.23</v>
       </c>
       <c r="F89" s="20" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G89" s="20" t="s">
         <v>21</v>
@@ -6002,19 +6023,19 @@
         <v>27</v>
       </c>
       <c r="B90" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C90" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D90" s="20" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E90" s="24">
         <v>9152.700000000001</v>
       </c>
       <c r="F90" s="20" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G90" s="20" t="s">
         <v>21</v>
@@ -6025,19 +6046,19 @@
         <v>27</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="E91" s="7">
         <v>1800.09</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G91" s="8" t="s">
         <v>21</v>
@@ -6048,19 +6069,19 @@
         <v>27</v>
       </c>
       <c r="B92" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C92" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D92" s="20" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E92" s="24">
         <v>45850.2</v>
       </c>
       <c r="F92" s="20" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G92" s="20" t="s">
         <v>21</v>
@@ -6071,19 +6092,19 @@
         <v>27</v>
       </c>
       <c r="B93" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C93" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D93" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E93" s="24">
         <v>5877.07</v>
       </c>
       <c r="F93" s="20" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G93" s="20" t="s">
         <v>21</v>
@@ -6094,19 +6115,19 @@
         <v>27</v>
       </c>
       <c r="B94" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D94" s="20" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E94" s="24">
         <v>29500.95</v>
       </c>
       <c r="F94" s="20" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G94" s="20" t="s">
         <v>21</v>
@@ -6117,19 +6138,19 @@
         <v>27</v>
       </c>
       <c r="B95" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C95" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D95" s="20" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="E95" s="24">
         <v>24174.03</v>
       </c>
       <c r="F95" s="20" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G95" s="20" t="s">
         <v>21</v>
@@ -6140,27 +6161,27 @@
         <v>27</v>
       </c>
       <c r="B96" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C96" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D96" s="20" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="E96" s="24">
         <v>111</v>
       </c>
       <c r="F96" s="20" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="G96" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="22" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B97" s="25"/>
       <c r="C97" s="25"/>
@@ -6176,19 +6197,19 @@
         <v>29</v>
       </c>
       <c r="B98" s="20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C98" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D98" s="20" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E98" s="24">
         <v>6499.56</v>
       </c>
       <c r="F98" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="G98" s="20" t="s">
         <v>23</v>
@@ -6199,19 +6220,19 @@
         <v>29</v>
       </c>
       <c r="B99" s="20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C99" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D99" s="20" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E99" s="24">
         <v>7600.38</v>
       </c>
       <c r="F99" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="G99" s="20" t="s">
         <v>23</v>
@@ -6222,19 +6243,19 @@
         <v>29</v>
       </c>
       <c r="B100" s="20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C100" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D100" s="20" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E100" s="24">
         <v>3750.63</v>
       </c>
       <c r="F100" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="G100" s="20" t="s">
         <v>23</v>
@@ -6245,19 +6266,19 @@
         <v>29</v>
       </c>
       <c r="B101" s="20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C101" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D101" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="E101" s="24">
         <v>4000.2</v>
       </c>
       <c r="F101" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="G101" s="20" t="s">
         <v>23</v>
@@ -6268,19 +6289,19 @@
         <v>29</v>
       </c>
       <c r="B102" s="20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C102" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D102" s="20" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E102" s="24">
         <v>41103.18</v>
       </c>
       <c r="F102" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="G102" s="20" t="s">
         <v>23</v>
@@ -6291,19 +6312,19 @@
         <v>29</v>
       </c>
       <c r="B103" s="20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C103" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D103" s="20" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E103" s="24">
         <v>76951.24000000001</v>
       </c>
       <c r="F103" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="G103" s="20" t="s">
         <v>23</v>
@@ -6314,19 +6335,19 @@
         <v>29</v>
       </c>
       <c r="B104" s="20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C104" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D104" s="20" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="E104" s="24">
         <v>53202.66</v>
       </c>
       <c r="F104" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="G104" s="20" t="s">
         <v>23</v>
@@ -6337,22 +6358,22 @@
         <v>29</v>
       </c>
       <c r="B105" s="20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C105" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D105" s="20" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E105" s="24">
         <v>100.01</v>
       </c>
       <c r="F105" s="20" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="G105" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -6360,19 +6381,19 @@
         <v>29</v>
       </c>
       <c r="B106" s="20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C106" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D106" s="20" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E106" s="24">
         <v>123758.99</v>
       </c>
       <c r="F106" s="20" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="G106" s="20" t="s">
         <v>25</v>
@@ -6383,19 +6404,19 @@
         <v>29</v>
       </c>
       <c r="B107" s="20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C107" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D107" s="20" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E107" s="24">
         <v>28001.4</v>
       </c>
       <c r="F107" s="20" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="G107" s="20" t="s">
         <v>25</v>
@@ -6406,22 +6427,22 @@
         <v>29</v>
       </c>
       <c r="B108" s="20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C108" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D108" s="20" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="E108" s="24">
         <v>249.99</v>
       </c>
       <c r="F108" s="20" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="G108" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -6429,19 +6450,19 @@
         <v>29</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C109" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D109" s="20" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E109" s="24">
         <v>201919.98</v>
       </c>
       <c r="F109" s="20" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="G109" s="20" t="s">
         <v>25</v>
@@ -6452,19 +6473,19 @@
         <v>29</v>
       </c>
       <c r="B110" s="20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C110" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D110" s="20" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E110" s="24">
         <v>19919.58</v>
       </c>
       <c r="F110" s="20" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="G110" s="20" t="s">
         <v>25</v>
@@ -6475,19 +6496,19 @@
         <v>29</v>
       </c>
       <c r="B111" s="20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C111" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D111" s="20" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E111" s="24">
         <v>30000.08</v>
       </c>
       <c r="F111" s="20" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="G111" s="20" t="s">
         <v>25</v>
@@ -6498,22 +6519,22 @@
         <v>29</v>
       </c>
       <c r="B112" s="20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C112" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D112" s="20" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="E112" s="24">
         <v>1920</v>
       </c>
       <c r="F112" s="20" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="G112" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -6521,27 +6542,27 @@
         <v>29</v>
       </c>
       <c r="B113" s="20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C113" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D113" s="20" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="E113" s="24">
         <v>259.98</v>
       </c>
       <c r="F113" s="20" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="22" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B114" s="25"/>
       <c r="C114" s="25"/>
@@ -6557,22 +6578,22 @@
         <v>31</v>
       </c>
       <c r="B115" s="20" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C115" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D115" s="20" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="E115" s="24">
         <v>430191.21</v>
       </c>
       <c r="F115" s="20" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="G115" s="20" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -6580,19 +6601,19 @@
         <v>31</v>
       </c>
       <c r="B116" s="20" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C116" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D116" s="20" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="E116" s="24">
         <v>180752.99</v>
       </c>
       <c r="F116" s="20" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="G116" s="20" t="s">
         <v>25</v>
@@ -6603,19 +6624,19 @@
         <v>31</v>
       </c>
       <c r="B117" s="20" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C117" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D117" s="20" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="E117" s="24">
         <v>287749.49</v>
       </c>
       <c r="F117" s="20" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="G117" s="20" t="s">
         <v>27</v>
@@ -6626,19 +6647,19 @@
         <v>31</v>
       </c>
       <c r="B118" s="20" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C118" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D118" s="20" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="E118" s="24">
         <v>106253.31</v>
       </c>
       <c r="F118" s="20" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="G118" s="20" t="s">
         <v>27</v>
@@ -6649,19 +6670,19 @@
         <v>31</v>
       </c>
       <c r="B119" s="20" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C119" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D119" s="20" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E119" s="24">
         <v>75172.14</v>
       </c>
       <c r="F119" s="20" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="G119" s="20" t="s">
         <v>27</v>
@@ -6672,19 +6693,19 @@
         <v>31</v>
       </c>
       <c r="B120" s="20" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C120" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D120" s="20" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E120" s="24">
         <v>13200.66</v>
       </c>
       <c r="F120" s="20" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="G120" s="20" t="s">
         <v>27</v>
@@ -6695,19 +6716,19 @@
         <v>31</v>
       </c>
       <c r="B121" s="20" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C121" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D121" s="20" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E121" s="24">
         <v>15000.04</v>
       </c>
       <c r="F121" s="20" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="G121" s="20" t="s">
         <v>27</v>
@@ -6718,22 +6739,22 @@
         <v>31</v>
       </c>
       <c r="B122" s="20" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C122" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D122" s="20" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E122" s="24">
         <v>379.97</v>
       </c>
       <c r="F122" s="20" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="G122" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -6741,22 +6762,22 @@
         <v>31</v>
       </c>
       <c r="B123" s="20" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C123" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D123" s="20" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="E123" s="24">
         <v>194.97</v>
       </c>
       <c r="F123" s="20" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="G123" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -6764,19 +6785,19 @@
         <v>31</v>
       </c>
       <c r="B124" s="20" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C124" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D124" s="20" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="E124" s="24">
         <v>59207.68</v>
       </c>
       <c r="F124" s="20" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="G124" s="20" t="s">
         <v>27</v>
@@ -6787,22 +6808,22 @@
         <v>31</v>
       </c>
       <c r="B125" s="20" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C125" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D125" s="20" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="E125" s="24">
         <v>49554.48</v>
       </c>
       <c r="F125" s="20" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="G125" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -6810,27 +6831,27 @@
         <v>31</v>
       </c>
       <c r="B126" s="20" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C126" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D126" s="20" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E126" s="24">
         <v>26081.3</v>
       </c>
       <c r="F126" s="20" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="G126" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="22" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B127" s="25"/>
       <c r="C127" s="25"/>
@@ -6846,19 +6867,19 @@
         <v>33</v>
       </c>
       <c r="B128" s="20" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C128" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D128" s="20" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E128" s="24">
         <v>55100.05</v>
       </c>
       <c r="F128" s="20" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="G128" s="20" t="s">
         <v>29</v>
@@ -6869,19 +6890,19 @@
         <v>33</v>
       </c>
       <c r="B129" s="20" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C129" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D129" s="20" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="E129" s="24">
         <v>293900.32</v>
       </c>
       <c r="F129" s="20" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="G129" s="20" t="s">
         <v>29</v>
@@ -6892,22 +6913,22 @@
         <v>33</v>
       </c>
       <c r="B130" s="20" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C130" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D130" s="20" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E130" s="24">
         <v>199.89</v>
       </c>
       <c r="F130" s="20" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="G130" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -6915,19 +6936,19 @@
         <v>33</v>
       </c>
       <c r="B131" s="20" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C131" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D131" s="20" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="E131" s="24">
         <v>7135.26</v>
       </c>
       <c r="F131" s="20" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="G131" s="20" t="s">
         <v>29</v>
@@ -6935,7 +6956,7 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="22" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B132" s="25"/>
       <c r="C132" s="25"/>
@@ -6957,7 +6978,7 @@
         <v>12869133.81</v>
       </c>
       <c r="F133" s="9" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="G133" s="9"/>
     </row>
@@ -7018,7 +7039,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7029,7 +7050,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="29" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -7043,22 +7064,22 @@
         <v>38</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>39</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -7066,7 +7087,7 @@
         <v>45</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>46</v>
@@ -7081,53 +7102,53 @@
         <v>0</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="20" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E6" s="24">
         <v>1678339.89</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="20" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E7" s="24">
         <v>237254</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -7135,22 +7156,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -7158,22 +7179,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -7181,22 +7202,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -7204,22 +7225,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -7227,22 +7248,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -7250,22 +7271,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -7273,22 +7294,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -7296,22 +7317,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -7319,7 +7340,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>51</v>
@@ -7334,7 +7355,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -7342,7 +7363,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>51</v>
@@ -7357,7 +7378,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -7365,22 +7386,22 @@
         <v>13</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -7388,22 +7409,22 @@
         <v>15</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E19" s="24">
         <v>360675.54</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -7411,22 +7432,22 @@
         <v>15</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -7434,7 +7455,7 @@
         <v>75</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>76</v>
@@ -7449,7 +7470,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -7457,22 +7478,22 @@
         <v>17</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E22" s="24">
         <v>657603.58</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -7480,22 +7501,22 @@
         <v>17</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -7503,22 +7524,22 @@
         <v>17</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E24" s="24">
         <v>127415</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -7526,7 +7547,7 @@
         <v>17</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>58</v>
@@ -7541,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -7564,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -7572,45 +7593,45 @@
         <v>17</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="C28" s="20" t="s">
+      <c r="B28" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="D28" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="E28" s="24">
-        <v>422847.85</v>
-      </c>
-      <c r="F28" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="G28" s="20" t="s">
-        <v>544</v>
+      <c r="C28" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1177614.62</v>
+      </c>
+      <c r="E28" s="14">
+        <v>1177614.62</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -7618,7 +7639,7 @@
         <v>19</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>62</v>
@@ -7633,7 +7654,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -7641,7 +7662,7 @@
         <v>19</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>71</v>
@@ -7656,30 +7677,30 @@
         <v>0</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>547</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>548</v>
+      <c r="B31" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D31" s="14">
+        <v>200510.82</v>
+      </c>
+      <c r="E31" s="14">
+        <v>200510.82</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -7687,22 +7708,22 @@
         <v>21</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E32" s="24">
         <v>429488</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -7710,7 +7731,7 @@
         <v>21</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>80</v>
@@ -7725,7 +7746,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -7733,7 +7754,7 @@
         <v>21</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>85</v>
@@ -7748,7 +7769,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -7756,7 +7777,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>89</v>
@@ -7771,98 +7792,98 @@
         <v>0</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="E36" s="20" t="s">
-        <v>554</v>
-      </c>
-      <c r="F36" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="G36" s="20" t="s">
-        <v>555</v>
+      <c r="B36" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="D36" s="14">
+        <v>208371.76</v>
+      </c>
+      <c r="E36" s="14">
+        <v>208371.76</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="20" t="s">
+      <c r="A37" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B37" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="G37" s="20" t="s">
-        <v>557</v>
+      <c r="B37" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="D37" s="14">
+        <v>325181.37</v>
+      </c>
+      <c r="E37" s="14">
+        <v>325181.37</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B38" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="E38" s="20" t="s">
-        <v>530</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="G38" s="20" t="s">
-        <v>558</v>
+      <c r="B38" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D38" s="14">
+        <v>599237.86</v>
+      </c>
+      <c r="E38" s="14">
+        <v>599237.86</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="20" t="s">
+      <c r="A39" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B39" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="G39" s="20" t="s">
+      <c r="B39" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D39" s="14">
+        <v>813547.03</v>
+      </c>
+      <c r="E39" s="14">
+        <v>813547.03</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="13" t="s">
         <v>560</v>
       </c>
     </row>
